--- a/xls/square_16_tri3_20.xlsx
+++ b/xls/square_16_tri3_20.xlsx
@@ -482,13 +482,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-2.336660920549353</v>
+        <v>-2.3366585932992043</v>
       </c>
       <c r="J20">
-        <v>-2.0912036612065683</v>
+        <v>-2.091203814348039</v>
       </c>
       <c r="K20">
-        <v>0.9641815365984747</v>
+        <v>0.9641766884222385</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -517,13 +517,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>-2.477724919816621</v>
+        <v>-2.4777267671115077</v>
       </c>
       <c r="J21">
-        <v>-1.995889644540517</v>
+        <v>-1.9958894565524663</v>
       </c>
       <c r="K21">
-        <v>1.6673150579370057</v>
+        <v>1.6673158985868353</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -552,13 +552,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-2.2552958588580436</v>
+        <v>-2.255294993771762</v>
       </c>
       <c r="J22">
-        <v>-1.8324692546766388</v>
+        <v>-1.8324693040298587</v>
       </c>
       <c r="K22">
-        <v>2.43099889104339</v>
+        <v>2.4309988268399354</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -587,13 +587,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-1.8742865807703823</v>
+        <v>-1.8742864214342312</v>
       </c>
       <c r="J23">
-        <v>-1.5169249959728133</v>
+        <v>-1.5169248966483726</v>
       </c>
       <c r="K23">
-        <v>3.328348886687472</v>
+        <v>3.3283488718337466</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -622,13 +622,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-0.7721250322164684</v>
+        <v>-0.7721250535335945</v>
       </c>
       <c r="J24">
-        <v>-0.6509431822891187</v>
+        <v>-0.6509431897480882</v>
       </c>
       <c r="K24">
-        <v>3.752652628376813</v>
+        <v>3.7526526282820076</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -657,13 +657,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-0.40043944420152483</v>
+        <v>-0.40043946356279614</v>
       </c>
       <c r="J25">
-        <v>-0.3244574770426554</v>
+        <v>-0.3244574900213246</v>
       </c>
       <c r="K25">
-        <v>3.900148520940518</v>
+        <v>3.900148533277392</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -692,13 +692,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-0.053988007247074046</v>
+        <v>-0.053988007499474425</v>
       </c>
       <c r="J26">
-        <v>-0.04907752716598439</v>
+        <v>-0.04907752737344242</v>
       </c>
       <c r="K26">
-        <v>3.7375614574202696</v>
+        <v>3.737561458956598</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -727,13 +727,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-0.0038807893921855756</v>
+        <v>-0.0038807893798567116</v>
       </c>
       <c r="J27">
-        <v>-0.003000994085663767</v>
+        <v>-0.003000994078377326</v>
       </c>
       <c r="K27">
-        <v>3.085948461036983</v>
+        <v>3.085948461054776</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -762,13 +762,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-0.00025373228000740913</v>
+        <v>-0.00025373228003437785</v>
       </c>
       <c r="J28">
-        <v>-0.0002047106799511012</v>
+        <v>-0.00020471067997469014</v>
       </c>
       <c r="K28">
-        <v>2.522354580753755</v>
+        <v>2.5223545808383</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -797,13 +797,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-0.004110380186086864</v>
+        <v>-0.004110380191315033</v>
       </c>
       <c r="J29">
-        <v>-0.003048611420543746</v>
+        <v>-0.003048611424218758</v>
       </c>
       <c r="K29">
-        <v>3.0442645448977905</v>
+        <v>3.044264545448584</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -832,13 +832,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-0.0006434194016853366</v>
+        <v>-0.0006434194026738857</v>
       </c>
       <c r="J30">
-        <v>-0.0005035079338864867</v>
+        <v>-0.0005035079345289911</v>
       </c>
       <c r="K30">
-        <v>2.71081424429715</v>
+        <v>2.7108142446897348</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -867,13 +867,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>9.29092864513174e-5</v>
+        <v>9.290928664876943e-5</v>
       </c>
       <c r="J31">
-        <v>2.9531959143728605e-5</v>
+        <v>2.9531959230705028e-5</v>
       </c>
       <c r="K31">
-        <v>2.252876994776799</v>
+        <v>2.252876995253279</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -902,13 +902,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-0.00034363409346926737</v>
+        <v>-0.0003436340935394777</v>
       </c>
       <c r="J32">
-        <v>-0.00026451114654132464</v>
+        <v>-0.00026451114656785983</v>
       </c>
       <c r="K32">
-        <v>2.5575625355925733</v>
+        <v>2.557562535319604</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_16_tri3_20.xlsx
+++ b/xls/square_16_tri3_20.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>441</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>289</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>361</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>1944</v>
+      </c>
+      <c r="I18">
+        <v>2.273994311857072</v>
+      </c>
+      <c r="J18">
+        <v>-0.9594727932563022</v>
+      </c>
+      <c r="K18">
+        <v>0.7076320327919748</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>441</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>289</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>400</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19">
+        <v>2166</v>
+      </c>
+      <c r="I19">
+        <v>0.6708581418940592</v>
+      </c>
+      <c r="J19">
+        <v>-1.8665097189921713</v>
+      </c>
+      <c r="K19">
+        <v>2.3885920168172756</v>
+      </c>
+    </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
         <v>11</v>
